--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8889</v>
+        <v>6.6667</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9003</v>
+        <v>2.7386</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>313.5556</v>
+        <v>270.7778</v>
       </c>
       <c r="D13" t="n">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="E13" t="n">
-        <v>91.10169999999999</v>
+        <v>109.167</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>989.8889</v>
+        <v>847.2222</v>
       </c>
       <c r="D14" t="n">
-        <v>958</v>
+        <v>815</v>
       </c>
       <c r="E14" t="n">
-        <v>155.0431</v>
+        <v>240.0889</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1435.1469</v>
+        <v>2723.7477</v>
       </c>
       <c r="D15" t="n">
-        <v>1516.2367</v>
+        <v>2439.1576</v>
       </c>
       <c r="E15" t="n">
-        <v>827.0078999999999</v>
+        <v>1430.972</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>47.1111</v>
+        <v>112.8889</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E16" t="n">
-        <v>28.7943</v>
+        <v>58.5543</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30.6592</v>
+        <v>24.138</v>
       </c>
       <c r="D17" t="n">
-        <v>28.9741</v>
+        <v>24.1478</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7005</v>
+        <v>2.3011</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03428217</v>
+        <v>0.02932336</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0358209</v>
+        <v>0.0281559</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00656847</v>
+        <v>0.00914184</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04317158</v>
+        <v>0.03663061</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04411697</v>
+        <v>0.03753166</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00439813</v>
+        <v>0.007931000000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.9693</v>
+        <v>2.8471</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4763</v>
+        <v>2.7514</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8884</v>
+        <v>1.0992</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>220.8889</v>
+        <v>203</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="E26" t="n">
-        <v>107.0321</v>
+        <v>116.5719</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>507.3333</v>
+        <v>540.5556</v>
       </c>
       <c r="D27" t="n">
-        <v>627</v>
+        <v>568</v>
       </c>
       <c r="E27" t="n">
-        <v>230.455</v>
+        <v>266.6117</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>351.7792</v>
+        <v>306.6534</v>
       </c>
       <c r="D28" t="n">
-        <v>333.7645</v>
+        <v>292.3503</v>
       </c>
       <c r="E28" t="n">
-        <v>104.3949</v>
+        <v>127.8372</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1119.6164</v>
+        <v>964.4395</v>
       </c>
       <c r="D29" t="n">
-        <v>1099.9159</v>
+        <v>937.7494</v>
       </c>
       <c r="E29" t="n">
-        <v>173.647</v>
+        <v>276.2947</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.7778</v>
+        <v>6.4444</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>3.3082</v>
+        <v>3.3208</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.2222</v>
+        <v>10.7778</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2.9907</v>
+        <v>3.5629</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>13.2222</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1794</v>
+        <v>4.0552</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.0947</v>
+        <v>6.4086</v>
       </c>
       <c r="D33" t="n">
-        <v>4.9833</v>
+        <v>6.4765</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3084</v>
+        <v>0.4389</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>46420</v>
+        <v>35500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04513983</v>
+        <v>0.03452098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>698</v>
+        <v>786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00067875</v>
+        <v>0.00076432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>711</v>
+        <v>192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>65.28830000000001</v>
+        <v>184.8958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.05110365</v>
+        <v>0.03927722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04513983</v>
+        <v>0.03452098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.7797</v>
+        <v>7.0431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1713,7 +1706,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46400</v>
+        <v>35500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1184 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24.9447</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.2682</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>49.8903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4987</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5013</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>2174</v>
-      </c>
-      <c r="C2" t="n">
-        <v>80.8669</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.2412</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.2947</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9518</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.4109</v>
-      </c>
-      <c r="I2" t="n">
-        <v>79.3965</v>
-      </c>
-      <c r="J2" t="n">
-        <v>270.8979</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>249</v>
-      </c>
-      <c r="N2" t="n">
-        <v>958</v>
-      </c>
-      <c r="O2" t="n">
-        <v>724.3524</v>
-      </c>
-      <c r="P2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>28.9741</v>
-      </c>
-      <c r="R2" t="n">
-        <v>210.066</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8595</v>
-      </c>
-      <c r="T2" t="n">
-        <v>21715</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.9616</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.02897033</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.04411697</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.3802</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>121</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>275</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>282.3209</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1099.9159</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.7619</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3447</v>
-      </c>
-      <c r="C3" t="n">
-        <v>90.3677</v>
-      </c>
-      <c r="D3" t="n">
-        <v>63.9486</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.4131</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.7066</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.4223</v>
-      </c>
-      <c r="I3" t="n">
-        <v>197.0592</v>
-      </c>
-      <c r="J3" t="n">
-        <v>916.9017</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>506</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1333</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1420.8103</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28.4162</v>
-      </c>
-      <c r="R3" t="n">
-        <v>363.4457</v>
-      </c>
-      <c r="S3" t="n">
-        <v>12097</v>
-      </c>
-      <c r="T3" t="n">
-        <v>29071</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.04182855</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.04585326</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.4763</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>735</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>574.6001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1504.3667</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.9736</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1883</v>
-      </c>
-      <c r="C4" t="n">
-        <v>69.2617</v>
-      </c>
-      <c r="D4" t="n">
-        <v>34.8694</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.9863</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9448</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5742</v>
-      </c>
-      <c r="I4" t="n">
-        <v>250.8327</v>
-      </c>
-      <c r="J4" t="n">
-        <v>340.47</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>300</v>
-      </c>
-      <c r="N4" t="n">
-        <v>926</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2529.8856</v>
-      </c>
-      <c r="P4" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>31.6236</v>
-      </c>
-      <c r="R4" t="n">
-        <v>184.7939</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7941</v>
-      </c>
-      <c r="T4" t="n">
-        <v>19515</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.03777862</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.04745068</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.788</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>241</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>739</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>333.7645</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1057.9331</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.5208</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2052</v>
-      </c>
-      <c r="C5" t="n">
-        <v>69.2015</v>
-      </c>
-      <c r="D5" t="n">
-        <v>39.4228</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.7554</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8219</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9112</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0622</v>
-      </c>
-      <c r="I5" t="n">
-        <v>388.6706</v>
-      </c>
-      <c r="J5" t="n">
-        <v>369.9386</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="n">
-        <v>348</v>
-      </c>
-      <c r="N5" t="n">
-        <v>934</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2573.6846</v>
-      </c>
-      <c r="P5" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27.3796</v>
-      </c>
-      <c r="R5" t="n">
-        <v>205.9655</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8333</v>
-      </c>
-      <c r="T5" t="n">
-        <v>20507</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.04176167</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.04554542</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4.8552</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>267</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>627</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>384.463</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1065.1758</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.9833</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2266</v>
-      </c>
-      <c r="C6" t="n">
-        <v>88.1613</v>
-      </c>
-      <c r="D6" t="n">
-        <v>35.5691</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.4786</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9021</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1324</v>
-      </c>
-      <c r="I6" t="n">
-        <v>473.0499</v>
-      </c>
-      <c r="J6" t="n">
-        <v>745.1911</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="n">
-        <v>336</v>
-      </c>
-      <c r="N6" t="n">
-        <v>995</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1754.8885</v>
-      </c>
-      <c r="P6" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>30.7875</v>
-      </c>
-      <c r="R6" t="n">
-        <v>241.9066</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9380</v>
-      </c>
-      <c r="T6" t="n">
-        <v>23807</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.0358209</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.04179443</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.8937</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>287</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>640</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>374.1493</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1127.3179</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.4732</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1344</v>
-      </c>
-      <c r="C7" t="n">
-        <v>87.6934</v>
-      </c>
-      <c r="D7" t="n">
-        <v>23.0299</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.8078</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9649</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.7764</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.2206</v>
-      </c>
-      <c r="I7" t="n">
-        <v>545.1897</v>
-      </c>
-      <c r="J7" t="n">
-        <v>876.8661</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>277</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1053</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1516.2367</v>
-      </c>
-      <c r="P7" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>28.6082</v>
-      </c>
-      <c r="R7" t="n">
-        <v>248.2498</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8529</v>
-      </c>
-      <c r="T7" t="n">
-        <v>21925</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.03247743</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.04802737</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.4169</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>128</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>343</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>309.7645</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1176.5605</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4.786</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1683</v>
-      </c>
-      <c r="C8" t="n">
-        <v>71.0123</v>
-      </c>
-      <c r="D8" t="n">
-        <v>31.3735</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.2634</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8971</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9355</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.0518</v>
-      </c>
-      <c r="I8" t="n">
-        <v>634.6803</v>
-      </c>
-      <c r="J8" t="n">
-        <v>198.3155</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>172</v>
-      </c>
-      <c r="N8" t="n">
-        <v>758</v>
-      </c>
-      <c r="O8" t="n">
-        <v>96.3553</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>24.0888</v>
-      </c>
-      <c r="R8" t="n">
-        <v>191.9655</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7943</v>
-      </c>
-      <c r="T8" t="n">
-        <v>21525</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.02165429</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.03521487</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.0837</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>73</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>99</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>189.9239</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>850.2813</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.7529</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2203</v>
-      </c>
-      <c r="C9" t="n">
-        <v>91.2092</v>
-      </c>
-      <c r="D9" t="n">
-        <v>31.4053</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.9043</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9389</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.9295</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="I9" t="n">
-        <v>734.3013999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>635.4403</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>348</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1040</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1601.526</v>
-      </c>
-      <c r="P9" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>37.2448</v>
-      </c>
-      <c r="R9" t="n">
-        <v>238.1076</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9212</v>
-      </c>
-      <c r="T9" t="n">
-        <v>24077</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03777681</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.04319475</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.3598</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>295</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>687</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>395.7056</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1165.3768</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.2694</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2633</v>
-      </c>
-      <c r="C10" t="n">
-        <v>93.5592</v>
-      </c>
-      <c r="D10" t="n">
-        <v>36.2778</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.579</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9218</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9454</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0457</v>
-      </c>
-      <c r="I10" t="n">
-        <v>780.5761</v>
-      </c>
-      <c r="J10" t="n">
-        <v>481.4953</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>286</v>
-      </c>
-      <c r="N10" t="n">
-        <v>912</v>
-      </c>
-      <c r="O10" t="n">
-        <v>698.5828</v>
-      </c>
-      <c r="P10" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>38.8102</v>
-      </c>
-      <c r="R10" t="n">
-        <v>242.9361</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9386</v>
-      </c>
-      <c r="T10" t="n">
-        <v>24420</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.03047091</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.03734644</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.4698</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>166</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>421</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>321.3209</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1029.6194</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.3308</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>531</v>
-      </c>
-      <c r="C11" t="n">
-        <v>28.7881</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24.8252</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.1596</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.5063</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9332</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1012.2844</v>
-      </c>
-      <c r="J11" t="n">
-        <v>184.8343</v>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>106</v>
-      </c>
-      <c r="N11" t="n">
-        <v>451</v>
-      </c>
-      <c r="O11" t="n">
-        <v>43.2426</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>43.2426</v>
-      </c>
-      <c r="R11" t="n">
-        <v>95.3909</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3354</v>
-      </c>
-      <c r="T11" t="n">
-        <v>9525</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.6102</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.5725</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.03160405</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.04734908</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.0483</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>112.1838</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>501.3036</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.3271</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2963,6 +2179,1197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2174</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80.8669</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.2412</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.2947</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9518</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="I2" t="n">
+        <v>79.3965</v>
+      </c>
+      <c r="J2" t="n">
+        <v>270.8979</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>242</v>
+      </c>
+      <c r="N2" t="n">
+        <v>815</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1024.4306</v>
+      </c>
+      <c r="P2" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>24.3912</v>
+      </c>
+      <c r="R2" t="n">
+        <v>210.066</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8595</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21715</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.0281559</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.03753166</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.9042</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>114</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>322</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>279.2498</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>937.7494</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.9711</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3447</v>
+      </c>
+      <c r="C3" t="n">
+        <v>90.3677</v>
+      </c>
+      <c r="D3" t="n">
+        <v>63.9486</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.4131</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="I3" t="n">
+        <v>197.0592</v>
+      </c>
+      <c r="J3" t="n">
+        <v>916.9017</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="n">
+        <v>471</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1283</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2439.1576</v>
+      </c>
+      <c r="P3" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22.7959</v>
+      </c>
+      <c r="R3" t="n">
+        <v>363.4457</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12097</v>
+      </c>
+      <c r="T3" t="n">
+        <v>29071</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03893527</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.04413333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.7514</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>421</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>914</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>547.0436999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1460.1118</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.4673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1883</v>
+      </c>
+      <c r="C4" t="n">
+        <v>69.2617</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.8694</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.9863</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="I4" t="n">
+        <v>250.8327</v>
+      </c>
+      <c r="J4" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>294</v>
+      </c>
+      <c r="N4" t="n">
+        <v>899</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4168.6543</v>
+      </c>
+      <c r="P4" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22.0564</v>
+      </c>
+      <c r="R4" t="n">
+        <v>184.7939</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7941</v>
+      </c>
+      <c r="T4" t="n">
+        <v>19515</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03702304</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04606713</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.3291</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>243</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>764</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>323.7939</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1029.8915</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6.8444</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2052</v>
+      </c>
+      <c r="C5" t="n">
+        <v>69.2015</v>
+      </c>
+      <c r="D5" t="n">
+        <v>39.4228</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.7554</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="I5" t="n">
+        <v>388.6706</v>
+      </c>
+      <c r="J5" t="n">
+        <v>369.9386</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>228</v>
+      </c>
+      <c r="N5" t="n">
+        <v>571</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4915.9944</v>
+      </c>
+      <c r="P5" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>26.1489</v>
+      </c>
+      <c r="R5" t="n">
+        <v>205.9655</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8333</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20507</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.02736109</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02784415</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.3986</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>189</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>505</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>250.2376</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>646.7716</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.9029</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2266</v>
+      </c>
+      <c r="C6" t="n">
+        <v>88.1613</v>
+      </c>
+      <c r="D6" t="n">
+        <v>35.5691</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.4786</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9021</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1324</v>
+      </c>
+      <c r="I6" t="n">
+        <v>473.0499</v>
+      </c>
+      <c r="J6" t="n">
+        <v>745.1911</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>339</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1012</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4467.3426</v>
+      </c>
+      <c r="P6" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>24.1478</v>
+      </c>
+      <c r="R6" t="n">
+        <v>241.9066</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9380</v>
+      </c>
+      <c r="T6" t="n">
+        <v>23807</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03614072</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.04250851</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.5472</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>295</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>746</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>378.9066</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1158.389</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1344</v>
+      </c>
+      <c r="C7" t="n">
+        <v>87.6934</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23.0299</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.8078</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7764</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="I7" t="n">
+        <v>545.1897</v>
+      </c>
+      <c r="J7" t="n">
+        <v>876.8661</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>162</v>
+      </c>
+      <c r="N7" t="n">
+        <v>771</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1688.5382</v>
+      </c>
+      <c r="P7" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>21.3739</v>
+      </c>
+      <c r="R7" t="n">
+        <v>248.2498</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8529</v>
+      </c>
+      <c r="T7" t="n">
+        <v>21925</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01899402</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03516534</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2085</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>182.6812</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>874.2813</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.7543</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1683</v>
+      </c>
+      <c r="C8" t="n">
+        <v>71.0123</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.3735</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.2634</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9355</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.0518</v>
+      </c>
+      <c r="I8" t="n">
+        <v>634.6803</v>
+      </c>
+      <c r="J8" t="n">
+        <v>198.3155</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>99</v>
+      </c>
+      <c r="N8" t="n">
+        <v>493</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1398.4012</v>
+      </c>
+      <c r="P8" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>191.9655</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7943</v>
+      </c>
+      <c r="T8" t="n">
+        <v>21525</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0124638</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0229036</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.0837</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>146</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>107.669</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>550.7889</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.5063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2203</v>
+      </c>
+      <c r="C9" t="n">
+        <v>91.2092</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31.4053</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.9043</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9295</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="I9" t="n">
+        <v>734.3013999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>635.4403</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>347</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1011</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1967.0601</v>
+      </c>
+      <c r="P9" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>27.3203</v>
+      </c>
+      <c r="R9" t="n">
+        <v>238.1076</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9212</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24077</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.03766826</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.04199028</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.5199</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>258</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>690</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>397.9483</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1148.6905</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.4765</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2633</v>
+      </c>
+      <c r="C10" t="n">
+        <v>93.5592</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36.2778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9218</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="I10" t="n">
+        <v>780.5761</v>
+      </c>
+      <c r="J10" t="n">
+        <v>481.4953</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>255</v>
+      </c>
+      <c r="N10" t="n">
+        <v>770</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2444.1505</v>
+      </c>
+      <c r="P10" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>27.1572</v>
+      </c>
+      <c r="R10" t="n">
+        <v>242.9361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9386</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24420</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02716812</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03153153</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.8814</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>182</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>568</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>292.3503</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>873.2813</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.7796</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>531</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28.7881</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24.8252</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.1596</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1012.2844</v>
+      </c>
+      <c r="J11" t="n">
+        <v>184.8343</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>79</v>
+      </c>
+      <c r="N11" t="n">
+        <v>410</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.8284</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.8284</v>
+      </c>
+      <c r="R11" t="n">
+        <v>95.3909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3354</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9525</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.6102</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02355397</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.04304462</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.0483</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>84.3553</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>467.061</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>6.0343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2983,7 +3390,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2187.2222</v>
+        <v>2322.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2174</v>
+        <v>2188.5</v>
       </c>
       <c r="E6" t="n">
-        <v>598.7996000000001</v>
+        <v>707.5599</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82.3704</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>87.6934</v>
+        <v>87.9273</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0353</v>
+        <v>32.8554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36.7931</v>
+        <v>36.1279</v>
       </c>
       <c r="D8" t="n">
-        <v>35.2412</v>
+        <v>35.0553</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1805</v>
+        <v>10.7489</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.387</v>
+        <v>2.7516</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2947</v>
+        <v>2.3867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6949</v>
+        <v>1.3263</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8811</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>0.9075</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0775</v>
+        <v>0.0803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.8685</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9295</v>
+        <v>0.9204</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0959</v>
+        <v>0.1053</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.6667</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7386</v>
+        <v>2.6667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>270.7778</v>
+        <v>283.2</v>
       </c>
       <c r="D13" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E13" t="n">
-        <v>109.167</v>
+        <v>121.6542</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>847.2222</v>
+        <v>841.7</v>
       </c>
       <c r="D14" t="n">
-        <v>815</v>
+        <v>834</v>
       </c>
       <c r="E14" t="n">
-        <v>240.0889</v>
+        <v>255.1318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2723.7477</v>
+        <v>2392.451</v>
       </c>
       <c r="D15" t="n">
-        <v>2439.1576</v>
+        <v>1743.5591</v>
       </c>
       <c r="E15" t="n">
-        <v>1430.972</v>
+        <v>2469.6639</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>112.8889</v>
+        <v>107.7</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>79.5</v>
       </c>
       <c r="E16" t="n">
-        <v>58.5543</v>
+        <v>111.9336</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.138</v>
+        <v>20.8378</v>
       </c>
       <c r="D17" t="n">
-        <v>24.1478</v>
+        <v>22.1141</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3011</v>
+        <v>9.8415</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>236.3819</v>
+        <v>254.3427</v>
       </c>
       <c r="D18" t="n">
-        <v>238.1076</v>
+        <v>240.0071</v>
       </c>
       <c r="E18" t="n">
-        <v>53.1676</v>
+        <v>75.75360000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9046.2222</v>
+        <v>9495.200000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>8595</v>
+        <v>8903.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1273.7742</v>
+        <v>1859.5788</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22951.3333</v>
+        <v>23331.5</v>
       </c>
       <c r="D20" t="n">
-        <v>21925</v>
+        <v>22866</v>
       </c>
       <c r="E20" t="n">
-        <v>2828.5609</v>
+        <v>2925.2437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.9969</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9957</v>
+        <v>0.9761</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0128</v>
+        <v>0.0633</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02932336</v>
+        <v>0.02907057</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0281559</v>
+        <v>0.02906571</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00914184</v>
+        <v>0.009006719999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03663061</v>
+        <v>0.03556791</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03753166</v>
+        <v>0.03594746</v>
       </c>
       <c r="E24" t="n">
-        <v>0.007931000000000001</v>
+        <v>0.00726084</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.8471</v>
+        <v>1.0675</v>
       </c>
       <c r="D25" t="n">
-        <v>2.7514</v>
+        <v>0.9615</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0992</v>
+        <v>0.7454</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>203</v>
+        <v>224.3</v>
       </c>
       <c r="D26" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="E26" t="n">
-        <v>116.5719</v>
+        <v>137.8454</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>540.5556</v>
+        <v>566.8</v>
       </c>
       <c r="D27" t="n">
-        <v>568</v>
+        <v>506</v>
       </c>
       <c r="E27" t="n">
-        <v>266.6117</v>
+        <v>325.281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>306.6534</v>
+        <v>319.4545</v>
       </c>
       <c r="D28" t="n">
-        <v>292.3503</v>
+        <v>298.3148</v>
       </c>
       <c r="E28" t="n">
-        <v>127.8372</v>
+        <v>141.0708</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>964.4395</v>
+        <v>956.5041</v>
       </c>
       <c r="D29" t="n">
-        <v>937.7494</v>
+        <v>955.2286</v>
       </c>
       <c r="E29" t="n">
-        <v>276.2947</v>
+        <v>290.0972</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.4444</v>
+        <v>6.9</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3.3208</v>
+        <v>3.9567</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.7778</v>
+        <v>10.7</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3.5629</v>
+        <v>3.653</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.2222</v>
+        <v>11.8</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>4.0552</v>
+        <v>3.7653</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.4086</v>
+        <v>7.238</v>
       </c>
       <c r="D33" t="n">
-        <v>6.4765</v>
+        <v>7.3845</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4389</v>
+        <v>0.4152</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1028360</v>
+        <v>1024824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35500</v>
+        <v>35628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03452098</v>
+        <v>0.03476499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>786</v>
+        <v>869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00076432</v>
+        <v>0.00084795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.72e-06</v>
+        <v>1.073e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>184.8958</v>
+        <v>209.5765</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03927722</v>
+        <v>0.03958983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03452098</v>
+        <v>0.03476499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>224</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03476499</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03498357</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.0431</v>
+        <v>7.7028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35500</v>
+        <v>35628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.9447</v>
+        <v>25.8878</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.2682</v>
+        <v>4.1785</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.8903</v>
+        <v>49.7517</v>
       </c>
     </row>
     <row r="12">
@@ -1949,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0487</v>
+        <v>50.0471</v>
       </c>
     </row>
     <row r="13">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4987</v>
+        <v>0.5163</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5013</v>
+        <v>0.4837</v>
       </c>
     </row>
     <row r="15">
@@ -2026,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2150,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2179,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="N2" t="n">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="O2" t="n">
-        <v>1024.4306</v>
+        <v>184.3381</v>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.3912</v>
+        <v>36.8676</v>
       </c>
       <c r="R2" t="n">
         <v>210.066</v>
@@ -2417,37 +2497,37 @@
         <v>0.9616</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0281559</v>
+        <v>0.02931937</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03753166</v>
+        <v>0.03799217</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9042</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AA2" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AB2" t="n">
-        <v>279.2498</v>
+        <v>291.3209</v>
       </c>
       <c r="AC2" t="n">
-        <v>937.7494</v>
+        <v>958.6905</v>
       </c>
       <c r="AD2" t="n">
         <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.9711</v>
+        <v>6.6122</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>471</v>
+        <v>518</v>
       </c>
       <c r="N3" t="n">
-        <v>1283</v>
+        <v>1368</v>
       </c>
       <c r="O3" t="n">
-        <v>2439.1576</v>
+        <v>4885.2127</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.7959</v>
+        <v>21.9068</v>
       </c>
       <c r="R3" t="n">
         <v>363.4457</v>
@@ -2518,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03893527</v>
+        <v>0.04282053</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04413333</v>
+        <v>0.0470572</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.7514</v>
+        <v>2.4763</v>
       </c>
       <c r="Z3" t="n">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="AA3" t="n">
-        <v>914</v>
+        <v>1167</v>
       </c>
       <c r="AB3" t="n">
-        <v>547.0436999999999</v>
+        <v>595.1147999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>1460.1118</v>
+        <v>1556.1535</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.4673</v>
+        <v>7.3395</v>
       </c>
     </row>
     <row r="4">
@@ -2586,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>294</v>
+        <v>166</v>
       </c>
       <c r="N4" t="n">
-        <v>899</v>
+        <v>570</v>
       </c>
       <c r="O4" t="n">
-        <v>4168.6543</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.0564</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>184.7939</v>
@@ -2619,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03702304</v>
+        <v>0.02090417</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04606713</v>
+        <v>0.0292083</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.3291</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>243</v>
+        <v>116</v>
       </c>
       <c r="AA4" t="n">
-        <v>764</v>
+        <v>384</v>
       </c>
       <c r="AB4" t="n">
-        <v>323.7939</v>
+        <v>181.6396</v>
       </c>
       <c r="AC4" t="n">
-        <v>1029.8915</v>
+        <v>645.9727</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.8444</v>
+        <v>7.4296</v>
       </c>
     </row>
     <row r="5">
@@ -2657,100 +2737,100 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2052</v>
+        <v>3536</v>
       </c>
       <c r="C5" t="n">
-        <v>69.2015</v>
+        <v>181.867</v>
       </c>
       <c r="D5" t="n">
-        <v>39.4228</v>
+        <v>30.1414</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7554</v>
+        <v>6.0338</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8219</v>
+        <v>0.9862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9112</v>
+        <v>0.7148</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0622</v>
+        <v>0.0738</v>
       </c>
       <c r="I5" t="n">
-        <v>388.6706</v>
+        <v>327.0461</v>
       </c>
       <c r="J5" t="n">
-        <v>369.9386</v>
+        <v>42.4075</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>228</v>
+        <v>390</v>
       </c>
       <c r="N5" t="n">
-        <v>571</v>
+        <v>907</v>
       </c>
       <c r="O5" t="n">
-        <v>4915.9944</v>
+        <v>6468.6088</v>
       </c>
       <c r="P5" t="n">
-        <v>188</v>
+        <v>299</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.1489</v>
+        <v>21.6341</v>
       </c>
       <c r="R5" t="n">
-        <v>205.9655</v>
+        <v>415.9899</v>
       </c>
       <c r="S5" t="n">
-        <v>8333</v>
+        <v>13536</v>
       </c>
       <c r="T5" t="n">
-        <v>20507</v>
+        <v>26753</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0.9687</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0.7992</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02736109</v>
+        <v>0.02881206</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02784415</v>
+        <v>0.03390274</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.3986</v>
+        <v>1.202</v>
       </c>
       <c r="Z5" t="n">
-        <v>189</v>
+        <v>379</v>
       </c>
       <c r="AA5" t="n">
-        <v>505</v>
+        <v>844</v>
       </c>
       <c r="AB5" t="n">
-        <v>250.2376</v>
+        <v>436.1909</v>
       </c>
       <c r="AC5" t="n">
-        <v>646.7716</v>
+        <v>1029.6488</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.9029</v>
+        <v>7.5552</v>
       </c>
     </row>
     <row r="6">
@@ -2758,61 +2838,61 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2266</v>
+        <v>2052</v>
       </c>
       <c r="C6" t="n">
-        <v>88.1613</v>
+        <v>69.2015</v>
       </c>
       <c r="D6" t="n">
-        <v>35.5691</v>
+        <v>39.4228</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4786</v>
+        <v>1.7554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.915</v>
+        <v>0.8219</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9021</v>
+        <v>0.9112</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1324</v>
+        <v>0.0622</v>
       </c>
       <c r="I6" t="n">
-        <v>473.0499</v>
+        <v>388.6706</v>
       </c>
       <c r="J6" t="n">
-        <v>745.1911</v>
+        <v>369.9386</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>339</v>
+        <v>265</v>
       </c>
       <c r="N6" t="n">
-        <v>1012</v>
+        <v>619</v>
       </c>
       <c r="O6" t="n">
-        <v>4467.3426</v>
+        <v>537.0732</v>
       </c>
       <c r="P6" t="n">
-        <v>185</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.1478</v>
+        <v>24.4124</v>
       </c>
       <c r="R6" t="n">
-        <v>241.9066</v>
+        <v>205.9655</v>
       </c>
       <c r="S6" t="n">
-        <v>9380</v>
+        <v>8333</v>
       </c>
       <c r="T6" t="n">
-        <v>23807</v>
+        <v>20507</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -2821,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03614072</v>
+        <v>0.03180127</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04250851</v>
+        <v>0.03018481</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.5472</v>
+        <v>0.971</v>
       </c>
       <c r="Z6" t="n">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="AA6" t="n">
-        <v>746</v>
+        <v>546</v>
       </c>
       <c r="AB6" t="n">
-        <v>378.9066</v>
+        <v>293.865</v>
       </c>
       <c r="AC6" t="n">
-        <v>1158.389</v>
+        <v>712.0265000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.975</v>
+        <v>7.098</v>
       </c>
     </row>
     <row r="7">
@@ -2859,61 +2939,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1344</v>
+        <v>2266</v>
       </c>
       <c r="C7" t="n">
-        <v>87.6934</v>
+        <v>88.1613</v>
       </c>
       <c r="D7" t="n">
-        <v>23.0299</v>
+        <v>35.5691</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8078</v>
+        <v>2.4786</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9649</v>
+        <v>0.915</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7764</v>
+        <v>0.9021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2206</v>
+        <v>0.1324</v>
       </c>
       <c r="I7" t="n">
-        <v>545.1897</v>
+        <v>473.0499</v>
       </c>
       <c r="J7" t="n">
-        <v>876.8661</v>
+        <v>745.1911</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>162</v>
+        <v>303</v>
       </c>
       <c r="N7" t="n">
-        <v>771</v>
+        <v>912</v>
       </c>
       <c r="O7" t="n">
-        <v>1688.5382</v>
+        <v>2767.8561</v>
       </c>
       <c r="P7" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.3739</v>
+        <v>22.3214</v>
       </c>
       <c r="R7" t="n">
-        <v>248.2498</v>
+        <v>241.9066</v>
       </c>
       <c r="S7" t="n">
-        <v>8529</v>
+        <v>9380</v>
       </c>
       <c r="T7" t="n">
-        <v>21925</v>
+        <v>23807</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -2922,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01899402</v>
+        <v>0.03230277</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03516534</v>
+        <v>0.03830806</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2085</v>
+        <v>2.0669</v>
       </c>
       <c r="Z7" t="n">
-        <v>68</v>
+        <v>269</v>
       </c>
       <c r="AA7" t="n">
-        <v>210</v>
+        <v>661</v>
       </c>
       <c r="AB7" t="n">
-        <v>182.6812</v>
+        <v>338.9361</v>
       </c>
       <c r="AC7" t="n">
-        <v>874.2813</v>
+        <v>1036.6783</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.7543</v>
+        <v>7.818</v>
       </c>
     </row>
     <row r="8">
@@ -2960,61 +3040,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1683</v>
+        <v>1344</v>
       </c>
       <c r="C8" t="n">
-        <v>71.0123</v>
+        <v>87.6934</v>
       </c>
       <c r="D8" t="n">
-        <v>31.3735</v>
+        <v>23.0299</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2634</v>
+        <v>3.8078</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8971</v>
+        <v>0.9649</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9355</v>
+        <v>0.7764</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0518</v>
+        <v>0.2206</v>
       </c>
       <c r="I8" t="n">
-        <v>634.6803</v>
+        <v>545.1897</v>
       </c>
       <c r="J8" t="n">
-        <v>198.3155</v>
+        <v>876.8661</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="N8" t="n">
-        <v>493</v>
+        <v>843</v>
       </c>
       <c r="O8" t="n">
-        <v>1398.4012</v>
+        <v>2513.1089</v>
       </c>
       <c r="P8" t="n">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.85</v>
+        <v>18.6156</v>
       </c>
       <c r="R8" t="n">
-        <v>191.9655</v>
+        <v>248.2498</v>
       </c>
       <c r="S8" t="n">
-        <v>7943</v>
+        <v>8529</v>
       </c>
       <c r="T8" t="n">
-        <v>21525</v>
+        <v>21925</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -3023,37 +3103,37 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0124638</v>
+        <v>0.02133896</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0229036</v>
+        <v>0.03844926</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.0837</v>
+        <v>0.4028</v>
       </c>
       <c r="Z8" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="AA8" t="n">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.669</v>
+        <v>201.6812</v>
       </c>
       <c r="AC8" t="n">
-        <v>550.7889</v>
+        <v>951.7666</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.5063</v>
+        <v>6.7112</v>
       </c>
     </row>
     <row r="9">
@@ -3061,61 +3141,61 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2203</v>
+        <v>1683</v>
       </c>
       <c r="C9" t="n">
-        <v>91.2092</v>
+        <v>71.0123</v>
       </c>
       <c r="D9" t="n">
-        <v>31.4053</v>
+        <v>31.3735</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9043</v>
+        <v>2.2634</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9389</v>
+        <v>0.8971</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9295</v>
+        <v>0.9355</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0832</v>
+        <v>-0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>734.3013999999999</v>
+        <v>634.6803</v>
       </c>
       <c r="J9" t="n">
-        <v>635.4403</v>
+        <v>198.3155</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>347</v>
+        <v>108</v>
       </c>
       <c r="N9" t="n">
-        <v>1011</v>
+        <v>503</v>
       </c>
       <c r="O9" t="n">
-        <v>1967.0601</v>
+        <v>10.8284</v>
       </c>
       <c r="P9" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.3203</v>
+        <v>10.8284</v>
       </c>
       <c r="R9" t="n">
-        <v>238.1076</v>
+        <v>191.9655</v>
       </c>
       <c r="S9" t="n">
-        <v>9212</v>
+        <v>7943</v>
       </c>
       <c r="T9" t="n">
-        <v>24077</v>
+        <v>21525</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -3124,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03766826</v>
+        <v>0.01359688</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04199028</v>
+        <v>0.02336818</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5199</v>
+        <v>0.5209</v>
       </c>
       <c r="Z9" t="n">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="AA9" t="n">
-        <v>690</v>
+        <v>153</v>
       </c>
       <c r="AB9" t="n">
-        <v>397.9483</v>
+        <v>117.0833</v>
       </c>
       <c r="AC9" t="n">
-        <v>1148.6905</v>
+        <v>561.6173</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.4765</v>
+        <v>6.7729</v>
       </c>
     </row>
     <row r="10">
@@ -3162,61 +3242,61 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2633</v>
+        <v>2203</v>
       </c>
       <c r="C10" t="n">
-        <v>93.5592</v>
+        <v>91.2092</v>
       </c>
       <c r="D10" t="n">
-        <v>36.2778</v>
+        <v>31.4053</v>
       </c>
       <c r="E10" t="n">
-        <v>2.579</v>
+        <v>2.9043</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9218</v>
+        <v>0.9389</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9454</v>
+        <v>0.9295</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0457</v>
+        <v>0.0832</v>
       </c>
       <c r="I10" t="n">
-        <v>780.5761</v>
+        <v>734.3013999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>481.4953</v>
+        <v>635.4403</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>255</v>
+        <v>383</v>
       </c>
       <c r="N10" t="n">
-        <v>770</v>
+        <v>1083</v>
       </c>
       <c r="O10" t="n">
-        <v>2444.1505</v>
+        <v>5583.4747</v>
       </c>
       <c r="P10" t="n">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.1572</v>
+        <v>23.9634</v>
       </c>
       <c r="R10" t="n">
-        <v>242.9361</v>
+        <v>238.1076</v>
       </c>
       <c r="S10" t="n">
-        <v>9386</v>
+        <v>9212</v>
       </c>
       <c r="T10" t="n">
-        <v>24420</v>
+        <v>24077</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -3225,37 +3305,37 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02716812</v>
+        <v>0.0415762</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03153153</v>
+        <v>0.04498069</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.8814</v>
+        <v>1.2599</v>
       </c>
       <c r="Z10" t="n">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="AA10" t="n">
-        <v>568</v>
+        <v>903</v>
       </c>
       <c r="AB10" t="n">
-        <v>292.3503</v>
+        <v>435.9483</v>
       </c>
       <c r="AC10" t="n">
-        <v>873.2813</v>
+        <v>1220.5483</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.7796</v>
+        <v>7.5455</v>
       </c>
     </row>
     <row r="11">
@@ -3263,99 +3343,200 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
+        <v>2633</v>
+      </c>
+      <c r="C11" t="n">
+        <v>93.5592</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.2778</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9218</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="I11" t="n">
+        <v>780.5761</v>
+      </c>
+      <c r="J11" t="n">
+        <v>481.4953</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>265</v>
+      </c>
+      <c r="N11" t="n">
+        <v>787</v>
+      </c>
+      <c r="O11" t="n">
+        <v>974.0092</v>
+      </c>
+      <c r="P11" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>27.8288</v>
+      </c>
+      <c r="R11" t="n">
+        <v>242.9361</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9386</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24420</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02823354</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03222768</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8233</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>186</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>466</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>302.7645</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>891.9382000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>7.498</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
         <v>531</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>28.7881</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>24.8252</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>1.1596</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>0.5063</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>0.9332</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.5942</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>1012.2844</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>184.8343</v>
       </c>
-      <c r="K11" t="b">
+      <c r="K12" t="b">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N12" t="n">
+        <v>410</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>95.3909</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3354</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9525</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.6102</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.02355397</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.04304462</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>84.3553</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>467.061</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>79</v>
-      </c>
-      <c r="N11" t="n">
-        <v>410</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5.8284</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.8284</v>
-      </c>
-      <c r="R11" t="n">
-        <v>95.3909</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3354</v>
-      </c>
-      <c r="T11" t="n">
-        <v>9525</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.6102</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.5725</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.02355397</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.04304462</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.0483</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>84.3553</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>467.061</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AE12" t="n">
         <v>3</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AF12" t="n">
         <v>7</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG12" t="n">
         <v>6.0343</v>
       </c>
     </row>

--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2322.1</v>
+        <v>2350.2</v>
       </c>
       <c r="D6" t="n">
         <v>2188.5</v>
       </c>
       <c r="E6" t="n">
-        <v>707.5599</v>
+        <v>668.9246000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92.31999999999999</v>
+        <v>91.56319999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>87.9273</v>
+        <v>84.5141</v>
       </c>
       <c r="E7" t="n">
-        <v>32.8554</v>
+        <v>33.0603</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36.1279</v>
+        <v>36.5948</v>
       </c>
       <c r="D8" t="n">
         <v>35.0553</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7489</v>
+        <v>10.2044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.7516</v>
+        <v>2.6601</v>
       </c>
       <c r="D9" t="n">
         <v>2.3867</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3263</v>
+        <v>1.276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="D10" t="n">
         <v>0.9075</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0803</v>
+        <v>0.078</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8685</v>
+        <v>0.8742</v>
       </c>
       <c r="D11" t="n">
         <v>0.9204</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1053</v>
+        <v>0.1013</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6667</v>
+        <v>2.6799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>283.2</v>
+        <v>242.3333</v>
       </c>
       <c r="D13" t="n">
-        <v>265</v>
+        <v>258.5</v>
       </c>
       <c r="E13" t="n">
-        <v>121.6542</v>
+        <v>145.7628</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>841.7</v>
+        <v>762.25</v>
       </c>
       <c r="D14" t="n">
-        <v>834</v>
+        <v>806</v>
       </c>
       <c r="E14" t="n">
-        <v>255.1318</v>
+        <v>299.5327</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2392.451</v>
+        <v>1993.7092</v>
       </c>
       <c r="D15" t="n">
-        <v>1743.5591</v>
+        <v>755.5412</v>
       </c>
       <c r="E15" t="n">
-        <v>2469.6639</v>
+        <v>2420.234</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>107.7</v>
+        <v>89.75</v>
       </c>
       <c r="D16" t="n">
-        <v>79.5</v>
+        <v>28.5</v>
       </c>
       <c r="E16" t="n">
-        <v>111.9336</v>
+        <v>109.5836</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.8378</v>
+        <v>17.3649</v>
       </c>
       <c r="D17" t="n">
-        <v>22.1141</v>
+        <v>21.7705</v>
       </c>
       <c r="E17" t="n">
-        <v>9.8415</v>
+        <v>12.0431</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>254.3427</v>
+        <v>221.0149</v>
       </c>
       <c r="D18" t="n">
-        <v>240.0071</v>
+        <v>219.6934</v>
       </c>
       <c r="E18" t="n">
-        <v>75.75360000000001</v>
+        <v>100.917</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9495.200000000001</v>
+        <v>8668.5</v>
       </c>
       <c r="D19" t="n">
-        <v>8903.5</v>
+        <v>8576.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1859.5788</v>
+        <v>2568.7569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23331.5</v>
+        <v>21815.6667</v>
       </c>
       <c r="D20" t="n">
-        <v>22866</v>
+        <v>21875</v>
       </c>
       <c r="E20" t="n">
-        <v>2925.2437</v>
+        <v>4394.013</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9969</v>
+        <v>0.9974</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9761</v>
+        <v>0.9801</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0633</v>
+        <v>0.058</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02907057</v>
+        <v>0.02560946</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02906571</v>
+        <v>0.0285228</v>
       </c>
       <c r="E23" t="n">
-        <v>0.009006719999999999</v>
+        <v>0.01185448</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03556791</v>
+        <v>0.03384685</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03594746</v>
+        <v>0.03306521</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00726084</v>
+        <v>0.00819932</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.0675</v>
+        <v>0.8924</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9615</v>
+        <v>0.8877</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7454</v>
+        <v>0.7902</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>224.3</v>
+        <v>187.5833</v>
       </c>
       <c r="D26" t="n">
-        <v>212</v>
+        <v>151</v>
       </c>
       <c r="E26" t="n">
-        <v>137.8454</v>
+        <v>150.9819</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>566.8</v>
+        <v>476.1667</v>
       </c>
       <c r="D27" t="n">
-        <v>506</v>
+        <v>425</v>
       </c>
       <c r="E27" t="n">
-        <v>325.281</v>
+        <v>361.7972</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>319.4545</v>
+        <v>273.5523</v>
       </c>
       <c r="D28" t="n">
-        <v>298.3148</v>
+        <v>292.5929</v>
       </c>
       <c r="E28" t="n">
-        <v>141.0708</v>
+        <v>167.0496</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>956.5041</v>
+        <v>867.2576</v>
       </c>
       <c r="D29" t="n">
-        <v>955.2286</v>
+        <v>920.0595</v>
       </c>
       <c r="E29" t="n">
-        <v>290.0972</v>
+        <v>338.9835</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.9</v>
+        <v>5.8333</v>
       </c>
       <c r="D30" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>3.9567</v>
+        <v>4.3658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.7</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>3.653</v>
+        <v>4.7162</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.8</v>
+        <v>10.4167</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3.7653</v>
+        <v>4.814</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.238</v>
+        <v>6.8669</v>
       </c>
       <c r="D33" t="n">
-        <v>7.3845</v>
+        <v>7.2188</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4152</v>
+        <v>1.0565</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1024824</v>
+        <v>1024062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35628</v>
+        <v>35600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03476499</v>
+        <v>0.03476352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00084795</v>
+        <v>0.00084858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.073e-05</v>
+        <v>1.269e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>209.5765</v>
+        <v>213.1737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03958983</v>
+        <v>0.03959204</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03476499</v>
+        <v>0.03476352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03476499</v>
+        <v>0.03476352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03498357</v>
+        <v>0.03498226</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7028</v>
+        <v>7.7041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35628</v>
+        <v>35600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.8878</v>
+        <v>25.8916</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.1785</v>
+        <v>4.502</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.7517</v>
+        <v>49.7543</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5163</v>
+        <v>0.5183</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4837</v>
+        <v>0.4817</v>
       </c>
     </row>
     <row r="15">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2259,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2874,7 +2874,7 @@
         <v>265</v>
       </c>
       <c r="N6" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="O6" t="n">
         <v>537.0732</v>
@@ -2892,7 +2892,7 @@
         <v>8333</v>
       </c>
       <c r="T6" t="n">
-        <v>20507</v>
+        <v>20013</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>0.03180127</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03018481</v>
+        <v>0.03077999</v>
       </c>
       <c r="Y6" t="n">
         <v>0.971</v>
@@ -2913,13 +2913,13 @@
         <v>238</v>
       </c>
       <c r="AA6" t="n">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AB6" t="n">
         <v>293.865</v>
       </c>
       <c r="AC6" t="n">
-        <v>712.0265000000001</v>
+        <v>707.7838</v>
       </c>
       <c r="AD6" t="n">
         <v>7</v>
@@ -3040,31 +3040,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1344</v>
+        <v>1625</v>
       </c>
       <c r="C8" t="n">
-        <v>87.6934</v>
+        <v>80.12479999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>23.0299</v>
+        <v>27.6985</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8078</v>
+        <v>2.8927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9649</v>
+        <v>0.9383</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7764</v>
+        <v>0.8325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2206</v>
+        <v>0.2321</v>
       </c>
       <c r="I8" t="n">
-        <v>545.1897</v>
+        <v>545.5717</v>
       </c>
       <c r="J8" t="n">
-        <v>876.8661</v>
+        <v>877.0762999999999</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -3073,10 +3073,10 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="N8" t="n">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="O8" t="n">
         <v>2513.1089</v>
@@ -3088,13 +3088,13 @@
         <v>18.6156</v>
       </c>
       <c r="R8" t="n">
-        <v>248.2498</v>
+        <v>229.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>8529</v>
+        <v>8558</v>
       </c>
       <c r="T8" t="n">
-        <v>21925</v>
+        <v>22035</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -3103,25 +3103,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02133896</v>
+        <v>0.02009815</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03844926</v>
+        <v>0.03798502</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4028</v>
+        <v>0.4361</v>
       </c>
       <c r="Z8" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="AA8" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AB8" t="n">
-        <v>201.6812</v>
+        <v>192.6812</v>
       </c>
       <c r="AC8" t="n">
-        <v>951.7666</v>
+        <v>948.1808</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
@@ -3133,7 +3133,7 @@
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.7112</v>
+        <v>6.9851</v>
       </c>
     </row>
     <row r="9">
@@ -3538,6 +3538,166 @@
       </c>
       <c r="AG12" t="n">
         <v>6.0343</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
+        <v>458.1205</v>
+      </c>
+      <c r="J13" t="n">
+        <v>481.0301</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>248</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>47.4558</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4187</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13513</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.0009553400000000001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0183527</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>292.8061</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.0322</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>857.4254</v>
+      </c>
+      <c r="J14" t="n">
+        <v>285.6159</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>82</v>
+      </c>
+      <c r="N14" t="n">
+        <v>491</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>80.22539999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4854</v>
+      </c>
+      <c r="T14" t="n">
+        <v>15344</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01689328</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.03199948</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>59</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>94.08329999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>557.0732</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.7164</v>
       </c>
     </row>
   </sheetData>

--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.5</v>
+        <v>4.3333</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6799</v>
+        <v>4.1194</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>242.3333</v>
+        <v>243.3333</v>
       </c>
       <c r="D13" t="n">
-        <v>258.5</v>
+        <v>261</v>
       </c>
       <c r="E13" t="n">
-        <v>145.7628</v>
+        <v>146.1819</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>762.25</v>
+        <v>765.9167</v>
       </c>
       <c r="D14" t="n">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="E14" t="n">
-        <v>299.5327</v>
+        <v>300.4525</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1993.7092</v>
+        <v>2356.8797</v>
       </c>
       <c r="D15" t="n">
-        <v>755.5412</v>
+        <v>1744.0235</v>
       </c>
       <c r="E15" t="n">
-        <v>2420.234</v>
+        <v>2164.1972</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>89.75</v>
+        <v>106.3333</v>
       </c>
       <c r="D16" t="n">
-        <v>28.5</v>
+        <v>95.5</v>
       </c>
       <c r="E16" t="n">
-        <v>109.5836</v>
+        <v>95.0352</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.3649</v>
+        <v>17.4789</v>
       </c>
       <c r="D17" t="n">
-        <v>21.7705</v>
+        <v>21.4958</v>
       </c>
       <c r="E17" t="n">
-        <v>12.0431</v>
+        <v>9.1546</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02560946</v>
+        <v>0.02571356</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0285228</v>
+        <v>0.02863362</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01185448</v>
+        <v>0.01189701</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03384685</v>
+        <v>0.03401309</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03306521</v>
+        <v>0.03312128</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00819932</v>
+        <v>0.008280640000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.8924</v>
+        <v>1.6316</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8877</v>
+        <v>1.5257</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7902</v>
+        <v>1.3339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>187.5833</v>
+        <v>188</v>
       </c>
       <c r="D26" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26" t="n">
-        <v>150.9819</v>
+        <v>151.5604</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>476.1667</v>
+        <v>495.75</v>
       </c>
       <c r="D27" t="n">
-        <v>425</v>
+        <v>504.5</v>
       </c>
       <c r="E27" t="n">
-        <v>361.7972</v>
+        <v>358.9655</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>273.5523</v>
+        <v>274.8571</v>
       </c>
       <c r="D28" t="n">
-        <v>292.5929</v>
+        <v>296.5072</v>
       </c>
       <c r="E28" t="n">
-        <v>167.0496</v>
+        <v>167.72</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>867.2576</v>
+        <v>872.1635</v>
       </c>
       <c r="D29" t="n">
         <v>920.0595</v>
       </c>
       <c r="E29" t="n">
-        <v>338.9835</v>
+        <v>340.6891</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.8669</v>
+        <v>6.9985</v>
       </c>
       <c r="D33" t="n">
-        <v>7.2188</v>
+        <v>7.2994</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0565</v>
+        <v>1.103</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35600</v>
+        <v>35656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03476352</v>
+        <v>0.0348182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00084858</v>
+        <v>0.00085249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213.1737</v>
+        <v>213.509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03959204</v>
+        <v>0.03965963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03476352</v>
+        <v>0.0348182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03476352</v>
+        <v>0.0348182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03498226</v>
+        <v>0.03503694</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7041</v>
+        <v>7.7284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35600</v>
+        <v>35656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>519</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.8916</v>
+        <v>26.0886</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.502</v>
+        <v>4.3014</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.7543</v>
+        <v>49.851</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5183</v>
+        <v>0.5288</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4817</v>
+        <v>0.4712</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2464,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="N2" t="n">
-        <v>825</v>
+        <v>859</v>
       </c>
       <c r="O2" t="n">
-        <v>184.3381</v>
+        <v>936.4773</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.8676</v>
+        <v>21.2836</v>
       </c>
       <c r="R2" t="n">
         <v>210.066</v>
@@ -2497,25 +2497,25 @@
         <v>0.9616</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02931937</v>
+        <v>0.02990111</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03799217</v>
+        <v>0.03955791</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.4281</v>
       </c>
       <c r="Z2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>318</v>
+        <v>543</v>
       </c>
       <c r="AB2" t="n">
-        <v>291.3209</v>
+        <v>299.1493</v>
       </c>
       <c r="AC2" t="n">
-        <v>958.6905</v>
+        <v>1006.3179</v>
       </c>
       <c r="AD2" t="n">
         <v>4</v>
@@ -2527,7 +2527,7 @@
         <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.6122</v>
+        <v>7.0427</v>
       </c>
     </row>
     <row r="3">
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>518</v>
@@ -2574,13 +2574,13 @@
         <v>1368</v>
       </c>
       <c r="O3" t="n">
-        <v>4885.2127</v>
+        <v>4580.3771</v>
       </c>
       <c r="P3" t="n">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.9068</v>
+        <v>21.7079</v>
       </c>
       <c r="R3" t="n">
         <v>363.4457</v>
@@ -2604,7 +2604,7 @@
         <v>0.0470572</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4763</v>
+        <v>3.5769</v>
       </c>
       <c r="Z3" t="n">
         <v>469</v>
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N4" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>980.3524</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>17.1992</v>
       </c>
       <c r="R4" t="n">
         <v>184.7939</v>
@@ -2699,25 +2699,25 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02090417</v>
+        <v>0.02115603</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0292083</v>
+        <v>0.02931079</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6234</v>
       </c>
       <c r="Z4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AA4" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AB4" t="n">
-        <v>181.6396</v>
+        <v>183.6396</v>
       </c>
       <c r="AC4" t="n">
-        <v>645.9727</v>
+        <v>647.9727</v>
       </c>
       <c r="AD4" t="n">
         <v>4</v>
@@ -2729,7 +2729,7 @@
         <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.4296</v>
+        <v>7.5801</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N5" t="n">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="O5" t="n">
-        <v>6468.6088</v>
+        <v>5598.026</v>
       </c>
       <c r="P5" t="n">
-        <v>299</v>
+        <v>252</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.6341</v>
+        <v>22.2144</v>
       </c>
       <c r="R5" t="n">
         <v>415.9899</v>
@@ -2800,25 +2800,25 @@
         <v>0.7992</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02881206</v>
+        <v>0.02903369</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03390274</v>
+        <v>0.03401488</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.202</v>
+        <v>1.9231</v>
       </c>
       <c r="Z5" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AA5" t="n">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="AB5" t="n">
-        <v>436.1909</v>
+        <v>440.8478</v>
       </c>
       <c r="AC5" t="n">
-        <v>1029.6488</v>
+        <v>1034.3057</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -2830,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.5552</v>
+        <v>7.7496</v>
       </c>
     </row>
     <row r="6">
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>265</v>
@@ -2877,13 +2877,13 @@
         <v>616</v>
       </c>
       <c r="O6" t="n">
-        <v>537.0732</v>
+        <v>3942.8553</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.4124</v>
+        <v>23.3305</v>
       </c>
       <c r="R6" t="n">
         <v>205.9655</v>
@@ -2907,7 +2907,7 @@
         <v>0.03077999</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.971</v>
+        <v>2.9131</v>
       </c>
       <c r="Z6" t="n">
         <v>238</v>
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N7" t="n">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="O7" t="n">
-        <v>2767.8561</v>
+        <v>3163.047</v>
       </c>
       <c r="P7" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.3214</v>
+        <v>22.7557</v>
       </c>
       <c r="R7" t="n">
         <v>241.9066</v>
@@ -3002,25 +3002,25 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03230277</v>
+        <v>0.0326226</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03830806</v>
+        <v>0.03847608</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.0669</v>
+        <v>4.1338</v>
       </c>
       <c r="Z7" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AA7" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AB7" t="n">
-        <v>338.9361</v>
+        <v>341.9361</v>
       </c>
       <c r="AC7" t="n">
-        <v>1036.6783</v>
+        <v>1041.0925</v>
       </c>
       <c r="AD7" t="n">
         <v>7</v>
@@ -3032,7 +3032,7 @@
         <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.818</v>
+        <v>8.135300000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3079,13 +3079,13 @@
         <v>837</v>
       </c>
       <c r="O8" t="n">
-        <v>2513.1089</v>
+        <v>2507.6947</v>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.6156</v>
+        <v>18.7141</v>
       </c>
       <c r="R8" t="n">
         <v>229.3209</v>
@@ -3171,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O9" t="n">
         <v>10.8284</v>
@@ -3204,25 +3204,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01359688</v>
+        <v>0.01347098</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02336818</v>
+        <v>0.02341463</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5209</v>
+        <v>1.0419</v>
       </c>
       <c r="Z9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB9" t="n">
-        <v>117.0833</v>
+        <v>115.2548</v>
       </c>
       <c r="AC9" t="n">
-        <v>561.6173</v>
+        <v>561.7889</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
@@ -3234,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.7729</v>
+        <v>7.2593</v>
       </c>
     </row>
     <row r="10">
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>383</v>
@@ -3281,13 +3281,13 @@
         <v>1083</v>
       </c>
       <c r="O10" t="n">
-        <v>5583.4747</v>
+        <v>5588.8889</v>
       </c>
       <c r="P10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.9634</v>
+        <v>23.8841</v>
       </c>
       <c r="R10" t="n">
         <v>238.1076</v>
@@ -3311,7 +3311,7 @@
         <v>0.04498069</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2599</v>
+        <v>1.6799</v>
       </c>
       <c r="Z10" t="n">
         <v>333</v>

--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.3333</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1194</v>
+        <v>4.7863</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>243.3333</v>
+        <v>290.75</v>
       </c>
       <c r="D13" t="n">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E13" t="n">
-        <v>146.1819</v>
+        <v>149.073</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>765.9167</v>
+        <v>879.8333</v>
       </c>
       <c r="D14" t="n">
-        <v>812</v>
+        <v>909.5</v>
       </c>
       <c r="E14" t="n">
-        <v>300.4525</v>
+        <v>271.1135</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2356.8797</v>
+        <v>2866.275</v>
       </c>
       <c r="D15" t="n">
-        <v>1744.0235</v>
+        <v>2446.8368</v>
       </c>
       <c r="E15" t="n">
-        <v>2164.1972</v>
+        <v>1881.4468</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>106.3333</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>95.5</v>
+        <v>128</v>
       </c>
       <c r="E16" t="n">
-        <v>95.0352</v>
+        <v>84.16759999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.4789</v>
+        <v>22.6074</v>
       </c>
       <c r="D17" t="n">
-        <v>21.4958</v>
+        <v>22.0078</v>
       </c>
       <c r="E17" t="n">
-        <v>9.1546</v>
+        <v>3.2287</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02571356</v>
+        <v>0.0319145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02863362</v>
+        <v>0.03250738</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01189701</v>
+        <v>0.01103876</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03401309</v>
+        <v>0.04000397</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03312128</v>
+        <v>0.04029398</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008280640000000001</v>
+        <v>0.00735801</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.6316</v>
+        <v>2.7051</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5257</v>
+        <v>2.2724</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3339</v>
+        <v>1.6299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>188</v>
+        <v>245.75</v>
       </c>
       <c r="D26" t="n">
-        <v>152</v>
+        <v>217.5</v>
       </c>
       <c r="E26" t="n">
-        <v>151.5604</v>
+        <v>160.2255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>495.75</v>
+        <v>656.75</v>
       </c>
       <c r="D27" t="n">
-        <v>504.5</v>
+        <v>693</v>
       </c>
       <c r="E27" t="n">
-        <v>358.9655</v>
+        <v>356.1461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>274.8571</v>
+        <v>329.306</v>
       </c>
       <c r="D28" t="n">
-        <v>296.5072</v>
+        <v>336.3062</v>
       </c>
       <c r="E28" t="n">
-        <v>167.72</v>
+        <v>170.9043</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>872.1635</v>
+        <v>1003.1156</v>
       </c>
       <c r="D29" t="n">
-        <v>920.0595</v>
+        <v>1030.6782</v>
       </c>
       <c r="E29" t="n">
-        <v>340.6891</v>
+        <v>309.6491</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.8333</v>
+        <v>7.4167</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4.3658</v>
+        <v>4.3996</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.333299999999999</v>
+        <v>10.0833</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>4.7162</v>
+        <v>4.4814</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10.4167</v>
+        <v>11.9167</v>
       </c>
       <c r="D32" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>4.814</v>
+        <v>4.2738</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.9985</v>
+        <v>7.1739</v>
       </c>
       <c r="D33" t="n">
-        <v>7.2994</v>
+        <v>7.3952</v>
       </c>
       <c r="E33" t="n">
-        <v>1.103</v>
+        <v>0.7556</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35656</v>
+        <v>38056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0348182</v>
+        <v>0.03716181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>873</v>
+        <v>942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00085249</v>
+        <v>0.00091987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213.509</v>
+        <v>239.3459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03965963</v>
+        <v>0.0423432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0348182</v>
+        <v>0.03716181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0348182</v>
+        <v>0.03716181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03503694</v>
+        <v>0.03738055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7284</v>
+        <v>7.8159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35656</v>
+        <v>38056</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>503</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.0886</v>
+        <v>23.967</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.3014</v>
+        <v>2.4142</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>49.851</v>
+        <v>47.3486</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5288</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4712</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.3257</v>
       </c>
     </row>
   </sheetData>
@@ -2464,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="N2" t="n">
-        <v>859</v>
+        <v>991</v>
       </c>
       <c r="O2" t="n">
-        <v>936.4773</v>
+        <v>1141.3423</v>
       </c>
       <c r="P2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.2836</v>
+        <v>22.8268</v>
       </c>
       <c r="R2" t="n">
         <v>210.066</v>
@@ -2497,37 +2497,37 @@
         <v>0.9616</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02990111</v>
+        <v>0.03315881</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03955791</v>
+        <v>0.04563666</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4281</v>
+        <v>2.3802</v>
       </c>
       <c r="Z2" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="AA2" t="n">
-        <v>543</v>
+        <v>714</v>
       </c>
       <c r="AB2" t="n">
-        <v>299.1493</v>
+        <v>330.8772</v>
       </c>
       <c r="AC2" t="n">
-        <v>1006.3179</v>
+        <v>1159.6438</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.0427</v>
+        <v>7.2304</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="N3" t="n">
-        <v>1368</v>
+        <v>1424</v>
       </c>
       <c r="O3" t="n">
-        <v>4580.3771</v>
+        <v>4738.2594</v>
       </c>
       <c r="P3" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.7079</v>
+        <v>21.2478</v>
       </c>
       <c r="R3" t="n">
         <v>363.4457</v>
@@ -2598,28 +2598,28 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04282053</v>
+        <v>0.04744978</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0470572</v>
+        <v>0.04898352</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.5769</v>
+        <v>4.1272</v>
       </c>
       <c r="Z3" t="n">
-        <v>469</v>
+        <v>570</v>
       </c>
       <c r="AA3" t="n">
-        <v>1167</v>
+        <v>1331</v>
       </c>
       <c r="AB3" t="n">
-        <v>595.1147999999999</v>
+        <v>664.8133</v>
       </c>
       <c r="AC3" t="n">
-        <v>1556.1535</v>
+        <v>1625.8519</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -2628,7 +2628,7 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.3395</v>
+        <v>7.1451</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>168</v>
+        <v>280</v>
       </c>
       <c r="N4" t="n">
-        <v>572</v>
+        <v>788</v>
       </c>
       <c r="O4" t="n">
-        <v>980.3524</v>
+        <v>2319.0084</v>
       </c>
       <c r="P4" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="Q4" t="n">
-        <v>17.1992</v>
+        <v>19.1654</v>
       </c>
       <c r="R4" t="n">
         <v>184.7939</v>
@@ -2699,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02115603</v>
+        <v>0.03526004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02931079</v>
+        <v>0.0403792</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6234</v>
+        <v>2.1646</v>
       </c>
       <c r="Z4" t="n">
-        <v>118</v>
+        <v>238</v>
       </c>
       <c r="AA4" t="n">
-        <v>386</v>
+        <v>672</v>
       </c>
       <c r="AB4" t="n">
-        <v>183.6396</v>
+        <v>308.6518</v>
       </c>
       <c r="AC4" t="n">
-        <v>647.9727</v>
+        <v>895.796</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.5801</v>
+        <v>7.5336</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="N5" t="n">
-        <v>910</v>
+        <v>933</v>
       </c>
       <c r="O5" t="n">
-        <v>5598.026</v>
+        <v>5626.097</v>
       </c>
       <c r="P5" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.2144</v>
+        <v>21.8066</v>
       </c>
       <c r="R5" t="n">
         <v>415.9899</v>
@@ -2800,25 +2800,25 @@
         <v>0.7992</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02903369</v>
+        <v>0.03073286</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03401488</v>
+        <v>0.03487459</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9231</v>
+        <v>2.6443</v>
       </c>
       <c r="Z5" t="n">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="AA5" t="n">
-        <v>847</v>
+        <v>870</v>
       </c>
       <c r="AB5" t="n">
-        <v>440.8478</v>
+        <v>464.6762</v>
       </c>
       <c r="AC5" t="n">
-        <v>1034.3057</v>
+        <v>1058.1341</v>
       </c>
       <c r="AD5" t="n">
         <v>13</v>
@@ -2830,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.7496</v>
+        <v>7.7063</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>265</v>
+        <v>377</v>
       </c>
       <c r="N6" t="n">
-        <v>616</v>
+        <v>952</v>
       </c>
       <c r="O6" t="n">
-        <v>3942.8553</v>
+        <v>4686.1172</v>
       </c>
       <c r="P6" t="n">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.3305</v>
+        <v>22.2091</v>
       </c>
       <c r="R6" t="n">
         <v>205.9655</v>
@@ -2901,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03180127</v>
+        <v>0.04524181</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03077999</v>
+        <v>0.04756908</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.9131</v>
+        <v>4.3697</v>
       </c>
       <c r="Z6" t="n">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="AA6" t="n">
-        <v>543</v>
+        <v>872</v>
       </c>
       <c r="AB6" t="n">
-        <v>293.865</v>
+        <v>420.8772</v>
       </c>
       <c r="AC6" t="n">
-        <v>707.7838</v>
+        <v>1093.6194</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.098</v>
+        <v>7.573</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="N7" t="n">
-        <v>916</v>
+        <v>1107</v>
       </c>
       <c r="O7" t="n">
-        <v>3163.047</v>
+        <v>3821.4167</v>
       </c>
       <c r="P7" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.7557</v>
+        <v>23.589</v>
       </c>
       <c r="R7" t="n">
         <v>241.9066</v>
@@ -3002,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0326226</v>
+        <v>0.04083156</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03847608</v>
+        <v>0.04649893</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1338</v>
+        <v>5.374</v>
       </c>
       <c r="Z7" t="n">
-        <v>272</v>
+        <v>355</v>
       </c>
       <c r="AA7" t="n">
-        <v>665</v>
+        <v>904</v>
       </c>
       <c r="AB7" t="n">
-        <v>341.9361</v>
+        <v>429.0488</v>
       </c>
       <c r="AC7" t="n">
-        <v>1041.0925</v>
+        <v>1255.7027</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>8.135300000000001</v>
+        <v>7.9356</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="N8" t="n">
-        <v>837</v>
+        <v>886</v>
       </c>
       <c r="O8" t="n">
-        <v>2507.6947</v>
+        <v>2574.6652</v>
       </c>
       <c r="P8" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.7141</v>
+        <v>19.0716</v>
       </c>
       <c r="R8" t="n">
         <v>229.3209</v>
@@ -3103,37 +3103,37 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02009815</v>
+        <v>0.02220145</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03798502</v>
+        <v>0.04020876</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4361</v>
+        <v>0.8721</v>
       </c>
       <c r="Z8" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="AA8" t="n">
-        <v>216</v>
+        <v>590</v>
       </c>
       <c r="AB8" t="n">
-        <v>192.6812</v>
+        <v>214.4092</v>
       </c>
       <c r="AC8" t="n">
-        <v>948.1808</v>
+        <v>1003.2224</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.9851</v>
+        <v>6.824</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N9" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="O9" t="n">
-        <v>10.8284</v>
+        <v>906.8843000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.8284</v>
+        <v>19.7149</v>
       </c>
       <c r="R9" t="n">
         <v>191.9655</v>
@@ -3204,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01347098</v>
+        <v>0.01435226</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02341463</v>
+        <v>0.0237863</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.0419</v>
+        <v>0.5209</v>
       </c>
       <c r="Z9" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="AA9" t="n">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="AB9" t="n">
-        <v>115.2548</v>
+        <v>126.7401</v>
       </c>
       <c r="AC9" t="n">
-        <v>561.7889</v>
+        <v>573.86</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.2593</v>
+        <v>7.4401</v>
       </c>
     </row>
     <row r="10">
@@ -3275,19 +3275,19 @@
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="N10" t="n">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="O10" t="n">
-        <v>5588.8889</v>
+        <v>5396.1071</v>
       </c>
       <c r="P10" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.8841</v>
+        <v>24.3068</v>
       </c>
       <c r="R10" t="n">
         <v>238.1076</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0415762</v>
+        <v>0.04233608</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04498069</v>
+        <v>0.04527142</v>
       </c>
       <c r="Y10" t="n">
         <v>1.6799</v>
       </c>
       <c r="Z10" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AA10" t="n">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="AB10" t="n">
-        <v>435.9483</v>
+        <v>444.1909</v>
       </c>
       <c r="AC10" t="n">
-        <v>1220.5483</v>
+        <v>1228.791</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
@@ -3335,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.5455</v>
+        <v>7.5257</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="N11" t="n">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="O11" t="n">
-        <v>974.0092</v>
+        <v>908.4529</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q11" t="n">
-        <v>27.8288</v>
+        <v>29.3049</v>
       </c>
       <c r="R11" t="n">
         <v>242.9361</v>
@@ -3406,25 +3406,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02823354</v>
+        <v>0.03185596</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03222768</v>
+        <v>0.03357903</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8233</v>
+        <v>1.2349</v>
       </c>
       <c r="Z11" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AA11" t="n">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="AB11" t="n">
-        <v>302.7645</v>
+        <v>341.7351</v>
       </c>
       <c r="AC11" t="n">
-        <v>891.9382000000001</v>
+        <v>930.3229</v>
       </c>
       <c r="AD11" t="n">
         <v>6</v>
@@ -3436,7 +3436,7 @@
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.498</v>
+        <v>7.3504</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3474,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="N12" t="n">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>26.4853</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>26.4853</v>
       </c>
       <c r="R12" t="n">
         <v>95.3909</v>
@@ -3507,37 +3507,37 @@
         <v>0.5725</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02355397</v>
+        <v>0.03190221</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04304462</v>
+        <v>0.04220472</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.0483</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AB12" t="n">
-        <v>84.3553</v>
+        <v>119.5685</v>
       </c>
       <c r="AC12" t="n">
-        <v>467.061</v>
+        <v>458.4752</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.0343</v>
+        <v>6.0162</v>
       </c>
     </row>
     <row r="13">
@@ -3554,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="N13" t="n">
-        <v>248</v>
+        <v>510</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>829.9675999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>27.6656</v>
       </c>
       <c r="R13" t="n">
         <v>47.4558</v>
@@ -3587,37 +3587,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0009553400000000001</v>
+        <v>0.01647958</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0183527</v>
+        <v>0.03774143</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1072</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>75.7696</v>
       </c>
       <c r="AC13" t="n">
-        <v>292.8061</v>
+        <v>593.328</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.0322</v>
+        <v>5.0201</v>
       </c>
     </row>
     <row r="14">
@@ -3634,22 +3634,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="N14" t="n">
-        <v>491</v>
+        <v>545</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1446.9819</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>20.38</v>
       </c>
       <c r="R14" t="n">
         <v>80.22539999999999</v>
@@ -3667,28 +3667,28 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01689328</v>
+        <v>0.02307375</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03199948</v>
+        <v>0.03551877</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>4.986</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="AA14" t="n">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="AB14" t="n">
-        <v>94.08329999999999</v>
+        <v>129.8823</v>
       </c>
       <c r="AC14" t="n">
-        <v>557.0732</v>
+        <v>619.1147999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.7164</v>
+        <v>6.803</v>
       </c>
     </row>
   </sheetData>

--- a/results/543_3/5_quantification/543_3_quantification.xlsx
+++ b/results/543_3/5_quantification/543_3_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7863</v>
+        <v>4.671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>290.75</v>
+        <v>325.5833</v>
       </c>
       <c r="D13" t="n">
-        <v>292</v>
+        <v>358</v>
       </c>
       <c r="E13" t="n">
-        <v>149.073</v>
+        <v>143.1639</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>879.8333</v>
+        <v>941.5</v>
       </c>
       <c r="D14" t="n">
-        <v>909.5</v>
+        <v>1003</v>
       </c>
       <c r="E14" t="n">
-        <v>271.1135</v>
+        <v>285.1132</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2866.275</v>
+        <v>3319.0448</v>
       </c>
       <c r="D15" t="n">
-        <v>2446.8368</v>
+        <v>2948.8572</v>
       </c>
       <c r="E15" t="n">
-        <v>1881.4468</v>
+        <v>1756.145</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>153.0833</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" t="n">
-        <v>84.16759999999999</v>
+        <v>84.10429999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6074</v>
+        <v>22.1358</v>
       </c>
       <c r="D17" t="n">
-        <v>22.0078</v>
+        <v>21.6998</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2287</v>
+        <v>2.0458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0319145</v>
+        <v>0.03667744</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03250738</v>
+        <v>0.0364641</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01103876</v>
+        <v>0.01018717</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04000397</v>
+        <v>0.04310532</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04029398</v>
+        <v>0.04424568</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00735801</v>
+        <v>0.009251260000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7051</v>
+        <v>3.1711</v>
       </c>
       <c r="D25" t="n">
-        <v>2.2724</v>
+        <v>3.5359</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6299</v>
+        <v>1.1133</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>245.75</v>
+        <v>288.6667</v>
       </c>
       <c r="D26" t="n">
-        <v>217.5</v>
+        <v>332.5</v>
       </c>
       <c r="E26" t="n">
-        <v>160.2255</v>
+        <v>149.5073</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>656.75</v>
+        <v>752.25</v>
       </c>
       <c r="D27" t="n">
-        <v>693</v>
+        <v>909.5</v>
       </c>
       <c r="E27" t="n">
-        <v>356.1461</v>
+        <v>370.4165</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>329.306</v>
+        <v>369.1527</v>
       </c>
       <c r="D28" t="n">
-        <v>336.3062</v>
+        <v>404.7914</v>
       </c>
       <c r="E28" t="n">
-        <v>170.9043</v>
+        <v>163.9836</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1003.1156</v>
+        <v>1072.9679</v>
       </c>
       <c r="D29" t="n">
-        <v>1030.6782</v>
+        <v>1142.5041</v>
       </c>
       <c r="E29" t="n">
-        <v>309.6491</v>
+        <v>323.9168</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.4167</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>4.3996</v>
+        <v>4.6677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.0833</v>
+        <v>11.0833</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4814</v>
+        <v>4.1442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.9167</v>
+        <v>13.5</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="E32" t="n">
-        <v>4.2738</v>
+        <v>4.5025</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.3333</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11.9418</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.1739</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.3952</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.7556</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.4443</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.6762</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9107</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38056</v>
+        <v>41269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03716181</v>
+        <v>0.04029932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>942</v>
+        <v>1070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00091987</v>
+        <v>0.00104486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>239.3459</v>
+        <v>276.9732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0423432</v>
+        <v>0.04591962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03716181</v>
+        <v>0.04029932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03716181</v>
+        <v>0.04029932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03738055</v>
+        <v>0.04051805</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.8159</v>
+        <v>7.9145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38056</v>
+        <v>41269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>626</v>
+        <v>752</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.967</v>
+        <v>23.3401</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +2117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.4142</v>
+        <v>2.6031</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.3486</v>
+        <v>47.0168</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.476</v>
+        <v>0.4707</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.524</v>
+        <v>0.5293</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="N2" t="n">
-        <v>991</v>
+        <v>1050</v>
       </c>
       <c r="O2" t="n">
-        <v>1141.3423</v>
+        <v>1380.053</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.8268</v>
+        <v>21.9056</v>
       </c>
       <c r="R2" t="n">
         <v>210.066</v>
@@ -2497,37 +2625,43 @@
         <v>0.9616</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03315881</v>
+        <v>0.0390925</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04563666</v>
+        <v>0.04835367</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3802</v>
+        <v>3.3323</v>
       </c>
       <c r="Z2" t="n">
-        <v>165</v>
+        <v>307</v>
       </c>
       <c r="AA2" t="n">
-        <v>714</v>
+        <v>905</v>
       </c>
       <c r="AB2" t="n">
-        <v>330.8772</v>
+        <v>385.4335</v>
       </c>
       <c r="AC2" t="n">
-        <v>1159.6438</v>
+        <v>1221.6144</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.2304</v>
+        <v>7.4363</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.4127</v>
       </c>
     </row>
     <row r="3">
@@ -2568,19 +2702,19 @@
         <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N3" t="n">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="O3" t="n">
-        <v>4738.2594</v>
+        <v>4508.2644</v>
       </c>
       <c r="P3" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.2478</v>
+        <v>20.3994</v>
       </c>
       <c r="R3" t="n">
         <v>363.4457</v>
@@ -2598,28 +2732,28 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04744978</v>
+        <v>0.04728445</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04898352</v>
+        <v>0.04905232</v>
       </c>
       <c r="Y3" t="n">
         <v>4.1272</v>
       </c>
       <c r="Z3" t="n">
-        <v>570</v>
+        <v>528</v>
       </c>
       <c r="AA3" t="n">
-        <v>1331</v>
+        <v>1231</v>
       </c>
       <c r="AB3" t="n">
-        <v>664.8133</v>
+        <v>659.1564</v>
       </c>
       <c r="AC3" t="n">
-        <v>1625.8519</v>
+        <v>1624.6093</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -2628,7 +2762,13 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.1451</v>
+        <v>7.2258</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3982</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="N4" t="n">
-        <v>788</v>
+        <v>1030</v>
       </c>
       <c r="O4" t="n">
-        <v>2319.0084</v>
+        <v>5869.8493</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>275</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.1654</v>
+        <v>21.3449</v>
       </c>
       <c r="R4" t="n">
         <v>184.7939</v>
@@ -2699,37 +2839,43 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03526004</v>
+        <v>0.04785292</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0403792</v>
+        <v>0.05277991</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.1646</v>
+        <v>4.3291</v>
       </c>
       <c r="Z4" t="n">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="AA4" t="n">
-        <v>672</v>
+        <v>1014</v>
       </c>
       <c r="AB4" t="n">
-        <v>308.6518</v>
+        <v>424.1493</v>
       </c>
       <c r="AC4" t="n">
-        <v>895.796</v>
+        <v>1175.661</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.5336</v>
+        <v>8.384600000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.4982</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
-        <v>416</v>
+        <v>458</v>
       </c>
       <c r="N5" t="n">
-        <v>933</v>
+        <v>976</v>
       </c>
       <c r="O5" t="n">
-        <v>5626.097</v>
+        <v>5652.896</v>
       </c>
       <c r="P5" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.8066</v>
+        <v>21.4939</v>
       </c>
       <c r="R5" t="n">
         <v>415.9899</v>
@@ -2800,37 +2946,43 @@
         <v>0.7992</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03073286</v>
+        <v>0.0338357</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03487459</v>
+        <v>0.03648189</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.6443</v>
+        <v>3.8462</v>
       </c>
       <c r="Z5" t="n">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="AA5" t="n">
-        <v>870</v>
+        <v>914</v>
       </c>
       <c r="AB5" t="n">
-        <v>464.6762</v>
+        <v>514.8894</v>
       </c>
       <c r="AC5" t="n">
-        <v>1058.1341</v>
+        <v>1109.3473</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
         <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.7063</v>
+        <v>8.1099</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4297</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +3020,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>377</v>
+        <v>225</v>
       </c>
       <c r="N6" t="n">
-        <v>952</v>
+        <v>726</v>
       </c>
       <c r="O6" t="n">
-        <v>4686.1172</v>
+        <v>1034.7788</v>
       </c>
       <c r="P6" t="n">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.2091</v>
+        <v>25.8695</v>
       </c>
       <c r="R6" t="n">
         <v>205.9655</v>
@@ -2901,37 +3053,43 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04524181</v>
+        <v>0.02700108</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04756908</v>
+        <v>0.03627642</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.3697</v>
+        <v>2.4276</v>
       </c>
       <c r="Z6" t="n">
-        <v>357</v>
+        <v>185</v>
       </c>
       <c r="AA6" t="n">
-        <v>872</v>
+        <v>518</v>
       </c>
       <c r="AB6" t="n">
-        <v>420.8772</v>
+        <v>250.3087</v>
       </c>
       <c r="AC6" t="n">
-        <v>1093.6194</v>
+        <v>831.5534</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.573</v>
+        <v>7.2282</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +3127,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="N7" t="n">
-        <v>1107</v>
+        <v>1130</v>
       </c>
       <c r="O7" t="n">
-        <v>3821.4167</v>
+        <v>3234.0298</v>
       </c>
       <c r="P7" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.589</v>
+        <v>22.1509</v>
       </c>
       <c r="R7" t="n">
         <v>241.9066</v>
@@ -3002,37 +3160,43 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04083156</v>
+        <v>0.04328358</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04649893</v>
+        <v>0.04746503</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.374</v>
+        <v>4.5472</v>
       </c>
       <c r="Z7" t="n">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="AA7" t="n">
-        <v>904</v>
+        <v>975</v>
       </c>
       <c r="AB7" t="n">
-        <v>429.0488</v>
+        <v>452.8772</v>
       </c>
       <c r="AC7" t="n">
-        <v>1255.7027</v>
+        <v>1279.0458</v>
       </c>
       <c r="AD7" t="n">
         <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.9356</v>
+        <v>8.100099999999999</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4658</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3234,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>190</v>
+        <v>426</v>
       </c>
       <c r="N8" t="n">
-        <v>886</v>
+        <v>1281</v>
       </c>
       <c r="O8" t="n">
-        <v>2574.6652</v>
+        <v>4505.039</v>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.0716</v>
+        <v>19.9338</v>
       </c>
       <c r="R8" t="n">
         <v>229.3209</v>
@@ -3103,37 +3267,43 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02220145</v>
+        <v>0.04977799</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04020876</v>
+        <v>0.05813479</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8721</v>
+        <v>2.1804</v>
       </c>
       <c r="Z8" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AA8" t="n">
-        <v>590</v>
+        <v>1180</v>
       </c>
       <c r="AB8" t="n">
-        <v>214.4092</v>
+        <v>490.6173</v>
       </c>
       <c r="AC8" t="n">
-        <v>1003.2224</v>
+        <v>1457.2418</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.824</v>
+        <v>6.8746</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.5664</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="N9" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="O9" t="n">
-        <v>906.8843000000001</v>
+        <v>1898.0652</v>
       </c>
       <c r="P9" t="n">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.7149</v>
+        <v>20.4093</v>
       </c>
       <c r="R9" t="n">
         <v>191.9655</v>
@@ -3204,25 +3374,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01435226</v>
+        <v>0.0168702</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0237863</v>
+        <v>0.02448316</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5209</v>
+        <v>1.5628</v>
       </c>
       <c r="Z9" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="AA9" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="AB9" t="n">
-        <v>126.7401</v>
+        <v>147.5685</v>
       </c>
       <c r="AC9" t="n">
-        <v>573.86</v>
+        <v>589.4457</v>
       </c>
       <c r="AD9" t="n">
         <v>3</v>
@@ -3231,10 +3401,16 @@
         <v>5</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4401</v>
+        <v>7.9116</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.3226</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="N10" t="n">
-        <v>1090</v>
+        <v>1115</v>
       </c>
       <c r="O10" t="n">
-        <v>5396.1071</v>
+        <v>5254.899</v>
       </c>
       <c r="P10" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.3068</v>
+        <v>23.1493</v>
       </c>
       <c r="R10" t="n">
         <v>238.1076</v>
@@ -3305,37 +3481,43 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04233608</v>
+        <v>0.04439861</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04527142</v>
+        <v>0.04630976</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6799</v>
+        <v>2.0999</v>
       </c>
       <c r="Z10" t="n">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="AA10" t="n">
-        <v>907</v>
+        <v>979</v>
       </c>
       <c r="AB10" t="n">
-        <v>444.1909</v>
+        <v>462.1909</v>
       </c>
       <c r="AC10" t="n">
-        <v>1228.791</v>
+        <v>1254.862</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.5257</v>
+        <v>7.7657</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.4758</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="N11" t="n">
         <v>820</v>
       </c>
       <c r="O11" t="n">
-        <v>908.4529</v>
+        <v>2008.4449</v>
       </c>
       <c r="P11" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="Q11" t="n">
-        <v>29.3049</v>
+        <v>25.4234</v>
       </c>
       <c r="R11" t="n">
         <v>242.9361</v>
@@ -3406,28 +3588,28 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03185596</v>
+        <v>0.03079054</v>
       </c>
       <c r="X11" t="n">
         <v>0.03357903</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2349</v>
+        <v>1.6465</v>
       </c>
       <c r="Z11" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="AA11" t="n">
-        <v>476</v>
+        <v>600</v>
       </c>
       <c r="AB11" t="n">
-        <v>341.7351</v>
+        <v>331.3209</v>
       </c>
       <c r="AC11" t="n">
-        <v>930.3229</v>
+        <v>931.9798</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
@@ -3436,7 +3618,13 @@
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.3504</v>
+        <v>7.8079</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1266</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3662,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="N12" t="n">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="O12" t="n">
-        <v>26.4853</v>
+        <v>872.0092</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="n">
-        <v>26.4853</v>
+        <v>20.7621</v>
       </c>
       <c r="R12" t="n">
         <v>95.3909</v>
@@ -3507,37 +3695,43 @@
         <v>0.5725</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03190221</v>
+        <v>0.0405486</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04220472</v>
+        <v>0.04766404</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.0483</v>
+        <v>2.0966</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="AA12" t="n">
-        <v>25</v>
+        <v>302</v>
       </c>
       <c r="AB12" t="n">
-        <v>119.5685</v>
+        <v>152.2254</v>
       </c>
       <c r="AC12" t="n">
-        <v>458.4752</v>
+        <v>514.5462</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.0162</v>
+        <v>6.1456</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.5476</v>
       </c>
     </row>
     <row r="13">
@@ -3554,22 +3748,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="N13" t="n">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="O13" t="n">
-        <v>829.9675999999999</v>
+        <v>2663.6846</v>
       </c>
       <c r="P13" t="n">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="Q13" t="n">
-        <v>27.6656</v>
+        <v>23.7829</v>
       </c>
       <c r="R13" t="n">
         <v>47.4558</v>
@@ -3587,37 +3781,43 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01647958</v>
+        <v>0.0284213</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03774143</v>
+        <v>0.0421816</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1072</v>
+        <v>4.2144</v>
       </c>
       <c r="Z13" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="n">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>75.7696</v>
+        <v>134.0538</v>
       </c>
       <c r="AC13" t="n">
-        <v>593.328</v>
+        <v>663.5412</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.0201</v>
+        <v>4.9003</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.3661</v>
       </c>
     </row>
     <row r="14">
@@ -3634,22 +3834,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="N14" t="n">
-        <v>545</v>
+        <v>647</v>
       </c>
       <c r="O14" t="n">
-        <v>1446.9819</v>
+        <v>1818.5332</v>
       </c>
       <c r="P14" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.38</v>
+        <v>19.7667</v>
       </c>
       <c r="R14" t="n">
         <v>80.22539999999999</v>
@@ -3667,37 +3867,43 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02307375</v>
+        <v>0.0315204</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03551877</v>
+        <v>0.04216632</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.986</v>
+        <v>3.7395</v>
       </c>
       <c r="Z14" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AA14" t="n">
-        <v>132</v>
+        <v>249</v>
       </c>
       <c r="AB14" t="n">
-        <v>129.8823</v>
+        <v>177.267</v>
       </c>
       <c r="AC14" t="n">
-        <v>619.1147999999999</v>
+        <v>736.7128</v>
       </c>
       <c r="AD14" t="n">
         <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.803</v>
+        <v>7.5868</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3804</v>
       </c>
     </row>
   </sheetData>
